--- a/Reports/Members/Kai Fong_Activity_Report.xlsx
+++ b/Reports/Members/Kai Fong_Activity_Report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,15 +440,25 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>Image Link</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -482,10 +492,20 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>View</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -514,20 +534,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Strava</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -561,15 +586,67 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>Strava</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-20 18:54:02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6.03</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -586,7 +663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -602,6 +679,11 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Total Steps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Total Points</t>
         </is>
       </c>
@@ -613,10 +695,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.39</v>
+        <v>17.42</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -631,6 +716,9 @@
       <c r="C3" t="n">
         <v>0</v>
       </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -644,6 +732,9 @@
       <c r="C4" t="n">
         <v>0</v>
       </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -661,6 +752,11 @@
           <t>---</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -669,10 +765,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.79</v>
+        <v>18.82</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Kai Fong_Activity_Report.xlsx
+++ b/Reports/Members/Kai Fong_Activity_Report.xlsx
@@ -440,25 +440,15 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Image Link</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Image Link</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -492,20 +482,10 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -701,7 +681,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -771,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Kai Fong_Activity_Report.xlsx
+++ b/Reports/Members/Kai Fong_Activity_Report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -627,6 +627,53 @@
         </is>
       </c>
       <c r="I5" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5/22/2026 8:02:19</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -675,7 +722,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.42</v>
+        <v>21.41</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -745,7 +792,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.82</v>
+        <v>22.81</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>

--- a/Reports/Members/Kai Fong_Activity_Report.xlsx
+++ b/Reports/Members/Kai Fong_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,15 +440,25 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>Image Link</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -457,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-14 23:28:39</t>
+          <t>2026-05-18 18:47:54</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -472,7 +482,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -482,10 +492,20 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>View</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -494,7 +514,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 18:47:54</t>
+          <t>2026-05-19 06:24:14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -504,12 +524,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -519,7 +539,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -541,7 +561,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-19 06:24:14</t>
+          <t>2026-05-20 18:54:02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -551,12 +571,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -566,7 +586,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -588,7 +608,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-20 18:54:02</t>
+          <t>5/22/2026 8:02:19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -603,7 +623,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -635,7 +655,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5/22/2026 8:02:19</t>
+          <t>2026-05-14 23:28:39</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -650,7 +670,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -660,20 +680,10 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -722,13 +732,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.41</v>
+        <v>15.79</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -792,13 +802,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.81</v>
+        <v>17.19</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Kai Fong_Activity_Report.xlsx
+++ b/Reports/Members/Kai Fong_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 18:47:54</t>
+          <t>2026-05-14 23:28:39</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,24 +482,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.77</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+          <t>5.62</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>View</t>
@@ -514,7 +506,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-19 06:24:14</t>
+          <t>2026-05-18 18:47:54</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -524,12 +516,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,7 +531,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -561,7 +553,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-20 18:54:02</t>
+          <t>2026-05-19 06:24:14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -571,12 +563,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -586,7 +578,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -608,7 +600,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5/22/2026 8:02:19</t>
+          <t>2026-05-20 18:54:02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -623,7 +615,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -655,7 +647,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-14 23:28:39</t>
+          <t>5/22/2026 8:02:19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -670,7 +662,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -680,10 +672,20 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>View</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -732,7 +734,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15.79</v>
+        <v>21.41</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -802,7 +804,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.19</v>
+        <v>22.81</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>

--- a/Reports/Members/Kai Fong_Activity_Report.xlsx
+++ b/Reports/Members/Kai Fong_Activity_Report.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5/22/2026 8:02:19</t>
+          <t>2026-05-22 08:02:19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -740,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -810,7 +810,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Kai Fong_Activity_Report.xlsx
+++ b/Reports/Members/Kai Fong_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-14 23:28:39</t>
+          <t>2026-05-18 18:47:54</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,16 +482,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.62</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>5.77</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>View</t>
@@ -506,7 +514,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 18:47:54</t>
+          <t>2026-05-19 06:24:14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -516,12 +524,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -553,7 +561,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-19 06:24:14</t>
+          <t>2026-05-20 18:54:02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -563,12 +571,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -600,7 +608,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-20 18:54:02</t>
+          <t>2026-05-22 08:02:19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -615,7 +623,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -647,7 +655,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-22 08:02:19</t>
+          <t>2026-05-25 18:46:04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -662,7 +670,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -686,6 +694,45 @@
         </is>
       </c>
       <c r="I6" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-14 23:28:39</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>5.62</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -734,7 +781,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.41</v>
+        <v>27.04</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -804,7 +851,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.81</v>
+        <v>28.44</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>

--- a/Reports/Members/Kai Fong_Activity_Report.xlsx
+++ b/Reports/Members/Kai Fong_Activity_Report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 18:47:54</t>
+          <t>2026-05-25 18:46:04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-19 06:24:14</t>
+          <t>2026-05-27 18:23:38</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-20 18:54:02</t>
+          <t>2026-05-29 17:48:24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Strava App</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-22 08:02:19</t>
+          <t>2026-05-18 18:47:54</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-25 18:46:04</t>
+          <t>2026-05-19 06:24:14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -665,12 +665,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-14 23:28:39</t>
+          <t>2026-05-20 18:54:02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -717,22 +717,124 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.62</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>6.03</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-22 08:02:19</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-01 08:14:08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6.31</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Strava App</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -781,7 +883,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.04</v>
+        <v>39.38</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -851,7 +953,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.44</v>
+        <v>40.78</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>

--- a/Reports/Members/Kai Fong_Activity_Report.xlsx
+++ b/Reports/Members/Kai Fong_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,7 +702,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-14 23:28:39</t>
+          <t>2026-05-27 18:23:38</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -717,22 +717,124 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.62</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>5.72</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-29 17:48:24</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>5.93</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Strava App</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-01 08:14:08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6.31</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Strava App</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -781,7 +883,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.04</v>
+        <v>39.38</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -851,7 +953,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.44</v>
+        <v>40.78</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>

--- a/Reports/Members/Kai Fong_Activity_Report.xlsx
+++ b/Reports/Members/Kai Fong_Activity_Report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -835,6 +835,53 @@
         </is>
       </c>
       <c r="I9" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>6/3/2026 18:46:11</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>5.77</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -883,13 +930,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.38</v>
+        <v>45.15</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -953,13 +1000,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40.78</v>
+        <v>46.55</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Kai Fong_Activity_Report.xlsx
+++ b/Reports/Members/Kai Fong_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 18:47:54</t>
+          <t>2026-05-25 18:46:04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-19 06:24:14</t>
+          <t>2026-05-27 18:23:38</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-20 18:54:02</t>
+          <t>2026-05-29 17:48:24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Strava App</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-22 08:02:19</t>
+          <t>2026-05-18 18:47:54</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-25 18:46:04</t>
+          <t>2026-05-19 06:24:14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -665,12 +665,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-27 18:23:38</t>
+          <t>2026-05-20 18:54:02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-29 17:48:24</t>
+          <t>2026-05-22 08:02:19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Strava App</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -882,6 +882,53 @@
         </is>
       </c>
       <c r="I10" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6/5/2026 18:50:59</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>5.58</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -930,13 +977,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45.15</v>
+        <v>50.73</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1000,13 +1047,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46.55</v>
+        <v>52.13</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Kai Fong_Activity_Report.xlsx
+++ b/Reports/Members/Kai Fong_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-25 18:46:04</t>
+          <t>2026-05-18 18:47:54</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-27 18:23:38</t>
+          <t>2026-05-19 06:24:14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-29 17:48:24</t>
+          <t>2026-05-20 18:54:02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Strava App</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-18 18:47:54</t>
+          <t>2026-05-22 08:02:19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-19 06:24:14</t>
+          <t>2026-05-25 18:46:04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -665,12 +665,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-20 18:54:02</t>
+          <t>2026-05-27 18:23:38</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-22 08:02:19</t>
+          <t>2026-05-29 17:48:24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Strava App</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">

--- a/Reports/Members/Kai Fong_Activity_Report.xlsx
+++ b/Reports/Members/Kai Fong_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 18:47:54</t>
+          <t>2026-05-25 18:46:04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-19 06:24:14</t>
+          <t>2026-05-27 18:23:38</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-20 18:54:02</t>
+          <t>2026-05-29 17:48:24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Strava App</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-22 08:02:19</t>
+          <t>2026-05-18 18:47:54</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-25 18:46:04</t>
+          <t>2026-05-19 06:24:14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -665,12 +665,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-27 18:23:38</t>
+          <t>2026-05-20 18:54:02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-29 17:48:24</t>
+          <t>2026-05-22 08:02:19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Strava App</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">

--- a/Reports/Members/Kai Fong_Activity_Report.xlsx
+++ b/Reports/Members/Kai Fong_Activity_Report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -929,6 +929,53 @@
         </is>
       </c>
       <c r="I11" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>6/10/2026 20:19:35</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>5.57</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -977,13 +1024,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50.73</v>
+        <v>56.3</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1047,13 +1094,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52.13</v>
+        <v>57.7</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Kai Fong_Activity_Report.xlsx
+++ b/Reports/Members/Kai Fong_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 18:47:54</t>
+          <t>2026-05-25 18:46:04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-19 06:24:14</t>
+          <t>2026-05-27 18:23:38</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-20 18:54:02</t>
+          <t>2026-05-29 17:48:24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Strava App</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-22 08:02:19</t>
+          <t>2026-05-18 18:47:54</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-25 18:46:04</t>
+          <t>2026-05-19 06:24:14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -665,12 +665,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-27 18:23:38</t>
+          <t>2026-05-20 18:54:02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-29 17:48:24</t>
+          <t>2026-05-22 08:02:19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Strava App</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -976,6 +976,53 @@
         </is>
       </c>
       <c r="I12" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>6/12/2026 7:52:55</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kai Fong</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1024,13 +1071,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>56.3</v>
+        <v>61.3</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1094,13 +1141,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>57.7</v>
+        <v>62.7</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
